--- a/EndResult/800m Fri.xlsx
+++ b/EndResult/800m Fri.xlsx
@@ -1919,12 +1919,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.16,05</t>
+          <t>10.15,78</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04.03.2011</t>
+          <t>28.04.2018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.15,78</t>
+          <t>10.16,05</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.04.2018</t>
+          <t>04.03.2011</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">

--- a/EndResult/800m Fri.xlsx
+++ b/EndResult/800m Fri.xlsx
@@ -1919,12 +1919,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.15,78</t>
+          <t>10.16,05</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>28.04.2018</t>
+          <t>04.03.2011</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.16,05</t>
+          <t>10.15,78</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>04.03.2011</t>
+          <t>28.04.2018</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
